--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
@@ -418,34 +418,34 @@
         </is>
       </c>
       <c r="B2">
-        <v>1125.71</v>
+        <v>1159.404</v>
       </c>
       <c r="C2">
-        <v>101.241</v>
+        <v>108.461</v>
       </c>
       <c r="D2">
-        <v>10.062</v>
+        <v>10.414</v>
       </c>
       <c r="E2">
-        <v>0.318</v>
+        <v>0.329</v>
       </c>
       <c r="F2">
-        <v>1105.429</v>
+        <v>1138.45</v>
       </c>
       <c r="G2">
-        <v>1144.87</v>
+        <v>1179.274</v>
       </c>
       <c r="H2">
-        <v>1105.575</v>
+        <v>1138.884</v>
       </c>
       <c r="I2">
-        <v>1145.108</v>
+        <v>1179.953</v>
       </c>
       <c r="J2">
-        <v>1105.751</v>
+        <v>1138.313</v>
       </c>
       <c r="K2">
-        <v>1145.285</v>
+        <v>1179.382</v>
       </c>
     </row>
     <row r="3">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="B3">
-        <v>1256.509</v>
+        <v>1294.12</v>
       </c>
       <c r="C3">
-        <v>128.417</v>
+        <v>138.335</v>
       </c>
       <c r="D3">
-        <v>11.332</v>
+        <v>11.762</v>
       </c>
       <c r="E3">
-        <v>0.358</v>
+        <v>0.372</v>
       </c>
       <c r="F3">
-        <v>1234.184</v>
+        <v>1270.985</v>
       </c>
       <c r="G3">
-        <v>1278.605</v>
+        <v>1317.09</v>
       </c>
       <c r="H3">
-        <v>1232.068</v>
+        <v>1269.097</v>
       </c>
       <c r="I3">
-        <v>1278.024</v>
+        <v>1316.534</v>
       </c>
       <c r="J3">
-        <v>1234.88</v>
+        <v>1271.623</v>
       </c>
       <c r="K3">
-        <v>1280.836</v>
+        <v>1319.06</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
@@ -418,34 +418,34 @@
         </is>
       </c>
       <c r="B2">
-        <v>1159.404</v>
+        <v>1177.294</v>
       </c>
       <c r="C2">
-        <v>108.461</v>
+        <v>122.62</v>
       </c>
       <c r="D2">
-        <v>10.414</v>
+        <v>11.073</v>
       </c>
       <c r="E2">
-        <v>0.329</v>
+        <v>0.35</v>
       </c>
       <c r="F2">
-        <v>1138.45</v>
+        <v>1155.155</v>
       </c>
       <c r="G2">
-        <v>1179.274</v>
+        <v>1198.562</v>
       </c>
       <c r="H2">
-        <v>1138.884</v>
+        <v>1154.107</v>
       </c>
       <c r="I2">
-        <v>1179.953</v>
+        <v>1198.925</v>
       </c>
       <c r="J2">
-        <v>1138.313</v>
+        <v>1155.227</v>
       </c>
       <c r="K2">
-        <v>1179.382</v>
+        <v>1200.045</v>
       </c>
     </row>
     <row r="3">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="B3">
-        <v>1294.12</v>
+        <v>1314.137</v>
       </c>
       <c r="C3">
-        <v>138.335</v>
+        <v>158.759</v>
       </c>
       <c r="D3">
-        <v>11.762</v>
+        <v>12.6</v>
       </c>
       <c r="E3">
-        <v>0.372</v>
+        <v>0.398</v>
       </c>
       <c r="F3">
-        <v>1270.985</v>
+        <v>1289.389</v>
       </c>
       <c r="G3">
-        <v>1317.09</v>
+        <v>1338.78</v>
       </c>
       <c r="H3">
-        <v>1269.097</v>
+        <v>1287.922</v>
       </c>
       <c r="I3">
-        <v>1316.534</v>
+        <v>1339.132</v>
       </c>
       <c r="J3">
-        <v>1271.623</v>
+        <v>1289.089</v>
       </c>
       <c r="K3">
-        <v>1319.06</v>
+        <v>1340.299</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
@@ -418,34 +418,34 @@
         </is>
       </c>
       <c r="B2">
-        <v>1177.294</v>
+        <v>1151.129</v>
       </c>
       <c r="C2">
-        <v>122.62</v>
+        <v>102.832</v>
       </c>
       <c r="D2">
-        <v>11.073</v>
+        <v>10.141</v>
       </c>
       <c r="E2">
-        <v>0.35</v>
+        <v>0.321</v>
       </c>
       <c r="F2">
-        <v>1155.155</v>
+        <v>1130.733</v>
       </c>
       <c r="G2">
-        <v>1198.562</v>
+        <v>1170.483</v>
       </c>
       <c r="H2">
-        <v>1154.107</v>
+        <v>1131.069</v>
       </c>
       <c r="I2">
-        <v>1198.925</v>
+        <v>1170.77</v>
       </c>
       <c r="J2">
-        <v>1155.227</v>
+        <v>1130.967</v>
       </c>
       <c r="K2">
-        <v>1200.045</v>
+        <v>1170.668</v>
       </c>
     </row>
     <row r="3">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="B3">
-        <v>1314.137</v>
+        <v>1284.841</v>
       </c>
       <c r="C3">
-        <v>158.759</v>
+        <v>131.33</v>
       </c>
       <c r="D3">
-        <v>12.6</v>
+        <v>11.46</v>
       </c>
       <c r="E3">
-        <v>0.398</v>
+        <v>0.362</v>
       </c>
       <c r="F3">
-        <v>1289.389</v>
+        <v>1262.402</v>
       </c>
       <c r="G3">
-        <v>1338.78</v>
+        <v>1307.324</v>
       </c>
       <c r="H3">
-        <v>1287.922</v>
+        <v>1260.972</v>
       </c>
       <c r="I3">
-        <v>1339.132</v>
+        <v>1307.621</v>
       </c>
       <c r="J3">
-        <v>1289.089</v>
+        <v>1262.083</v>
       </c>
       <c r="K3">
-        <v>1340.299</v>
+        <v>1308.733</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
@@ -418,34 +418,34 @@
         </is>
       </c>
       <c r="B2">
-        <v>1151.129</v>
+        <v>1184.197</v>
       </c>
       <c r="C2">
-        <v>102.832</v>
+        <v>118.797</v>
       </c>
       <c r="D2">
-        <v>10.141</v>
+        <v>10.899</v>
       </c>
       <c r="E2">
-        <v>0.321</v>
+        <v>0.345</v>
       </c>
       <c r="F2">
-        <v>1130.733</v>
+        <v>1162.373</v>
       </c>
       <c r="G2">
-        <v>1170.483</v>
+        <v>1205.098</v>
       </c>
       <c r="H2">
-        <v>1131.069</v>
+        <v>1161.388</v>
       </c>
       <c r="I2">
-        <v>1170.77</v>
+        <v>1205.029</v>
       </c>
       <c r="J2">
-        <v>1130.967</v>
+        <v>1162.904</v>
       </c>
       <c r="K2">
-        <v>1170.668</v>
+        <v>1206.544</v>
       </c>
     </row>
     <row r="3">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="B3">
-        <v>1284.841</v>
+        <v>1321.845</v>
       </c>
       <c r="C3">
-        <v>131.33</v>
+        <v>153.239</v>
       </c>
       <c r="D3">
-        <v>11.46</v>
+        <v>12.379</v>
       </c>
       <c r="E3">
-        <v>0.362</v>
+        <v>0.391</v>
       </c>
       <c r="F3">
-        <v>1262.402</v>
+        <v>1297.499</v>
       </c>
       <c r="G3">
-        <v>1307.324</v>
+        <v>1346.024</v>
       </c>
       <c r="H3">
-        <v>1260.972</v>
+        <v>1295.8</v>
       </c>
       <c r="I3">
-        <v>1307.621</v>
+        <v>1345.726</v>
       </c>
       <c r="J3">
-        <v>1262.083</v>
+        <v>1297.881</v>
       </c>
       <c r="K3">
-        <v>1308.733</v>
+        <v>1347.807</v>
       </c>
     </row>
   </sheetData>
